--- a/data/processed/harmonization/Physical__Thermal_conductivity/10.5440_1417652/10.5440_1417652_soil_Physical__Thermal_conductivity.xlsx
+++ b/data/processed/harmonization/Physical__Thermal_conductivity/10.5440_1417652/10.5440_1417652_soil_Physical__Thermal_conductivity.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
@@ -440,8 +440,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,11 +501,6 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>source_row</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>notes</t>
         </is>
       </c>
@@ -524,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:10</t>
+          <t>CN_MM71:CPIT1:10</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -557,12 +551,9 @@
         <v>-163.7033</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -579,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:18</t>
+          <t>CN_MM71:CPIT1:18</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -612,12 +603,9 @@
         <v>-163.7033</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -634,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:30</t>
+          <t>CN_MM71:CPIT1:30</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,12 +655,9 @@
         <v>-163.7033</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -689,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:48</t>
+          <t>CN_MM71:CPIT1:48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -722,12 +707,9 @@
         <v>-163.7033</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -744,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:5</t>
+          <t>CN_MM71:CPIT3:5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -777,12 +759,9 @@
         <v>-163.6975</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -799,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:20</t>
+          <t>CN_MM71:CPIT3:20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -832,12 +811,9 @@
         <v>-163.6975</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -854,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:40</t>
+          <t>CN_MM71:CPIT3:40</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -887,12 +863,9 @@
         <v>-163.6975</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -909,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:15</t>
+          <t>CN_MM71:CPIT4:15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -942,12 +915,9 @@
         <v>-163.6926</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -964,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:40</t>
+          <t>CN_MM71:CPIT4:40</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -997,12 +967,9 @@
         <v>-163.6926</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -1019,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:56</t>
+          <t>CN_MM71:CPIT4:56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1052,12 +1019,9 @@
         <v>-163.6926</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:65</t>
+          <t>CN_MM71:CPIT4:65</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1107,12 +1071,9 @@
         <v>-163.6926</v>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
